--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE30"/>
+  <dimension ref="A1:AE31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -4064,6 +4064,142 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2">
+        <v>46082</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0100a</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10.1177/00222194261417592</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>University Students With Specific Learning Disabilities: Do Soft Skills and Study-Related Factors Make a Difference to Their Academic Outcomes?</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Understanding the role of individual factors associated with positive academic outcomes is fundamental to providing effective support for students with specific learning disabilities (SLDs) throughout their academic careers. The present study aimed to investigate group differences between students with and without SLDs and to examine the relationships between study-related factors, social, emotional, and behavioral (SEB) skills, and student outcomes (achievement, academic and life satisfaction, and burnout) in a sample of 752 university students (133 male</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>JOURNAL OF LEARNING DISABILITIES</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Pellegrino, Gerardo and Feraco, Tommaso and De Vita, Francesca and Martino, Maria Grazia and Matteucci, Maria Cristina and Montesano, Lorena and Passolunghi, Maria Chiara and Re, Anna Maria and Sini, Barbara and Tinti, Carla and Valenti, Antonella and Meneghetti, Chiara and Carretti, Barbara</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Pellegrino et al.</t>
+        </is>
+      </c>
+      <c r="K31">
+        <v>2026</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>academicachievement; schoolsatisfaction; disabilities</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>gerardo.pellegrino@phd.unipd.it</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>https://osf.io/69q84/</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>22.28</t>
+        </is>
+      </c>
+      <c r="V31">
+        <v>752</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>young_adult</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>learning disabilities</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>review</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -3952,9 +3952,14 @@
           <t>0095</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0095a</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3964,7 +3969,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Experiental features of volunteering predict changes in college studentsâ€™ social, emotional, and behavioral skills</t>
+          <t>Experiental features of volunteering predict changes in college students' social, emotional, and behavioral skills</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4002,7 +4007,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>volunteering</t>
+          <t>volunteering; skilldevelopment</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">

--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -3964,7 +3964,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10.1016/j.jrp.2026.104705</t>
+          <t>https://doi.org/10.1016/j.jrp.2026.104705</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10.1177/00222194261417592</t>
+          <t>https://doi.org/10.1177/00222194261417592</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">

--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE34"/>
+  <dimension ref="A1:AE36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>academicachievement; schoolsatisfaction; disabilities</t>
+          <t>academicachievement; schoolsatisfaction; learningdisabilities</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4593,6 +4593,268 @@
         </is>
       </c>
       <c r="AC34" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0113</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0113</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/09388982261452122</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Social, Emotional, and Behavioral Skills of Students With Specific Learning Disabilities: A Replication, Extension, and Synthesis of Existing Research</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Social, emotional, and behavioral (SEB) skills have been found to predict academic and non-academic outcomes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>LEARNING DISABILITIES RESEARCH \&amp; PRACTICE</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Feraco, Tommaso and Pellegrino, Gerardo and Bonelli, Roberta and Da Re, Lorenza and Carretti, Barbara and Meneghetti, Chiara</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Feraco et al.</t>
+        </is>
+      </c>
+      <c r="K35">
+        <v>2026</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>noNewData</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>academicachievement; learningdisabilities; learningfactors; positiveschooloutcomes</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>tommaso.feraco@unipd.it</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.17605/OSF.IO/BJ4E5</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>18.23</t>
+        </is>
+      </c>
+      <c r="V35">
+        <v>5075</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>school_age</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>clinical</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>learning disabilities</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0114</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0114</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/08902070261444881</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Does the `Maturity Principle' Hold for Social, Emotional, and Behavioral Skills? A Study on Age Differences From 18 to 65</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>The maturity principle posits that socially desirable personality traits, such as agreeableness, conscientiousness, and emotional stability, tend to increase across adulthood. This study examined whether this principle extends to social, emotional, and behavioral (SEB) skills by investigating age differences in a representative sample of N = 940 German adults (age range: 18-65, mean age = 43, SD = 14, 50 \% female) using moderated non-linear factor analysis models and comparing them to age differences in Big Five traits in a demographically comparable sample. Additionally, we explored age-specific associations between SEB skills and life quality, measured by life satisfaction and self-rated health. Contrary to the widely accepted maturity principle, we found few corresponding age differences in SEB skills, whereas the expected age-related patterns were evident in Big Five traits. These results remained consistent regardless of the level of measurement invariance. Some skills showed lower mean levels in older adults, and skill variances differed with age. In conclusion, these findings suggest that the maturity principle known from the Big Five literature does not fully generalize to SEB skills. This cross-sectional study lays the groundwork for future longitudinal research on SEB skills and highlights the importance of considering individuals within context.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>EUROPEAN JOURNAL OF PERSONALITY</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Jalynskij, Maria and Neyer, Franz J. and Lechner, Clemens M.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Jalynskij et  al.</t>
+        </is>
+      </c>
+      <c r="K36">
+        <v>2026</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>noNewData</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>normativechange; age</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>maria.jalynskij@uni-jena.de</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://osf.io/ne6xk/files/</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>43.34</t>
+        </is>
+      </c>
+      <c r="V36">
+        <v>1008</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>bessi192</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>bf</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
         <is>
           <t>TF</t>
         </is>

--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE36"/>
+  <dimension ref="A1:AE39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -4860,6 +4860,351 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0118a</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.learninstruc.2026.102415</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Using board games as a protective tool: Effects on cognitive, social, emotional, behavioural outcomes, and learning</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Introduction: Board games are increasingly used in school settings as engaging, structured activities that can foster executive functions (EFs) and learning. However, their effects on Social, Emotional, and Behavioural (SEB) skills remain unexplored. Aims: This study aimed to examine the effects of a 10-week teacher-led board game intervention, integrated with metacognitive activities, on EFs, SEB skills, and learning in primary school. Sample: A total of 150 fourth- and fifth-grade students from socioeconomically diverse backgrounds participated (83 in the intervention group</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>LEARNING AND INSTRUCTION</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Cravet, Elena and Usai, Maria Carmen</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Cravet &amp; Usai</t>
+        </is>
+      </c>
+      <c r="K37">
+        <v>2026</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>interventions; skilldevelopment</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>elenacravet.mail@gmail.com</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://osf.io/97p5a/overview?view_only=2268b108c44a44dfb8746ca8139426b6</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>48.7</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V37">
+        <v>150</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>children</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0119</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0119</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/27000710241257381</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Social, emotional, and behavioral skills can be integrated into existing dynamic personality models</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>We are very excited by the recent work of Soto and colleagues (2021</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Personality Science</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Jayawickreme, Eranda and Fleeson, William</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Jayawickreme &amp; Fleeson</t>
+        </is>
+      </c>
+      <c r="K38">
+        <v>2024</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>theorydevelopment</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>jayawide@wfu.edu</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0120a</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/27000710261450451</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Am I More Skilled than I Think? Investigating the Agreement Between Self- and Informant-Reports of Social, Emotional, and Behavioural Skills in Brazil</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>This paper explores self- and informant-reports of social, emotional, and behavioral (SEB) skills and the cross-cultural adaptation of the Behavioral, Emotional, and Social Skills Inventory (BESSI) in Brazil. Study 1 (N = 185) examined self-informant agreement of SEB skills and assessed BESSIâ€™s internal structure (N = 1,049). Study 2 (N = 123) focused on the convergence of BESSIâ€™s domain and facet scores with personality variables and tested their temporal stability. The results showed that (1) informant-reports had higher means than self-reports, (2) agreement was higher for the Social Engagement domain and lower for the Innovation domain, and (3) BESSI demonstrated strong validity and reliability evidence for use in Brazil. In sum, BESSIâ€™s domains and facets were accurately perceived by informants.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Personality Science</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Fernandes, Marcelle and Zanon, Cristian and SÃ¡, Lucas G. C. and Fabretti, Rodrigo R. and Cruz, Ana C. A. and Silva, TaÃ­s B. and Sewell, Madison N. and Napolitano, Christopher M. and Soto, Christopher and Roberts, Brent W.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Fernandes et al.</t>
+        </is>
+      </c>
+      <c r="K39">
+        <v>2026</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>missingData</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>skillassessment;selfreport;languageadaptation;otherreport</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>cristian.zanon@ufrgs.br</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://osf.io/7efmp/overview</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>60.3</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>29.9</t>
+        </is>
+      </c>
+      <c r="V39">
+        <v>1103</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>bessi192</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>GP</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>184 participants with informant reports</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -5128,7 +5128,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>missingData</t>
+          <t>include</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>both</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">

--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE39"/>
+  <dimension ref="A1:AE44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -5205,6 +5205,510 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0123</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0123</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/educsci16071148</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Teachers' Socio-Emotional Competencies in the Digital Era: Cross-Cultural Adaptation and Psychometric Validation of the BESSI in Kazakhstan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Education Sciences</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Rakhimbekova, Assel and Shora, Nurym and Yessingeldinov, Baurzhan and Shilibekova, Aidana</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Rakhimbekova et al.</t>
+        </is>
+      </c>
+      <c r="K40">
+        <v>2026</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>noValidatedMeasure</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>skillassessment;selfreport;languageadaptation</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>assel.e.rakhimbekova@gmail.com</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="V40">
+        <v>918</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0124</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>0124</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/pmh.70087</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Assumptions and Consequences of Different Conceptualizations of Personality Functioning</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Personality and Mental Health</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Hopwood, Christopher J.</t>
+        </is>
+      </c>
+      <c r="K41">
+        <v>2026</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>personalityfunctioning</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>chopwoodmsu@gmail.com</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0126</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0126a</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.paid.2026.113970</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motivation to change personality across adulthood: Preferences for human and digital assistance in representative Swiss samples</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Personality and Individual Differences</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Allemand, Mathias and Olaru, Gabriel and Hill, Patrick L.</t>
+        </is>
+      </c>
+      <c r="K42">
+        <v>2026</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>mathias.allemand@phsh.ch</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>http://dx.doi.org/10.48573/z3z3-y672</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>cross</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>52.67</t>
+        </is>
+      </c>
+      <c r="V42">
+        <v>1898</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>bessi192</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>preferenceforhumanvsdigital excluded because not continuous</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>0128a</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/01461672261461318</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>To Regulate or Not to Regulate? Situational and Individual Differences in Emotion Regulation Initiation in Daily Life</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PERSONALITY AND SOCIAL PSYCHOLOGY BULLETIN</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Springstein, Tabea and Bankston, Anna C. and English, Tammy</t>
+        </is>
+      </c>
+      <c r="K43">
+        <v>2026</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>skilluse; esm; emotionregulation</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>tabea.springstein@ucr.edu</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>19.73</t>
+        </is>
+      </c>
+      <c r="V43">
+        <v>215</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>young_adult</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>not_clinical</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>bessi45</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>esm study</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0129</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0129</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1177/08902070261467477</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>The Living SEB Skills Project: A Living Resource for Review and Meta-Analysis of Social, Emotional, and Behavioral Skills</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>EUROPEAN JOURNAL OF PERSONALITY</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Feraco, Tommaso and Calderan, Margherita and Pellegrino, Gerardo</t>
+        </is>
+      </c>
+      <c r="K44">
+        <v>2026</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>include</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>noNewData</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>metaanalysis; theorydevelopment</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>tommaso.feraco@unipd.it</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.19101246</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>TF</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>living metaanalysis</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/3.meta_data/review_data/review_data.xlsx
+++ b/data/3.meta_data/review_data/review_data.xlsx
@@ -5350,6 +5350,11 @@
           <t>Hopwood, Christopher J.</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Hopwood</t>
+        </is>
+      </c>
       <c r="K41">
         <v>2026</v>
       </c>
@@ -5423,6 +5428,11 @@
           <t>Allemand, Mathias and Olaru, Gabriel and Hill, Patrick L.</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Allemand et al.</t>
+        </is>
+      </c>
       <c r="K42">
         <v>2026</v>
       </c>
@@ -5434,6 +5444,11 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>include</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>changegoals; volitionalchange</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -5544,6 +5559,11 @@
           <t>Springstein, Tabea and Bankston, Anna C. and English, Tammy</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Springstein et al.</t>
+        </is>
+      </c>
       <c r="K43">
         <v>2026</v>
       </c>
@@ -5663,6 +5683,11 @@
       <c r="I44" t="inlineStr">
         <is>
           <t>Feraco, Tommaso and Calderan, Margherita and Pellegrino, Gerardo</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Feraco et al.</t>
         </is>
       </c>
       <c r="K44">
